--- a/data/monthly/【2025年8月】月次数値.xlsx
+++ b/data/monthly/【2025年8月】月次数値.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -23,19 +23,10 @@
     <t>レポート終了日</t>
   </si>
   <si>
-    <t>広告セット名</t>
-  </si>
-  <si>
-    <t>プラットフォーム</t>
-  </si>
-  <si>
-    <t>配置</t>
-  </si>
-  <si>
-    <t>デバイスプラットフォーム</t>
-  </si>
-  <si>
-    <t>広告セットの配信</t>
+    <t>キャンペーン名</t>
+  </si>
+  <si>
+    <t>キャンペーンの配信</t>
   </si>
   <si>
     <t>アトリビューション設定</t>
@@ -68,9 +59,6 @@
     <t>終了日時</t>
   </si>
   <si>
-    <t>開始</t>
-  </si>
-  <si>
     <t>インプレッション</t>
   </si>
   <si>
@@ -104,7 +92,49 @@
     <t>ランディングページビューの単価 (JPY)</t>
   </si>
   <si>
-    <t>No data available.</t>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【はんだ歯科｜スタッフ募集中✨】...</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>クリックから7日間、または表示から1日間</t>
+  </si>
+  <si>
+    <t>1日</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>Instagram投稿: おいしいクレープ屋さんがあなたの街に！！</t>
+  </si>
+  <si>
+    <t>archived</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（マウスピース矯正）</t>
+  </si>
+  <si>
+    <t>not_delivering</t>
+  </si>
+  <si>
+    <t>広告セット予算を使用</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美ジルコニア）</t>
   </si>
 </sst>
 </file>
@@ -459,10 +489,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -538,22 +568,205 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>160</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
-      <c r="A2" t="s">
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
         <v>29</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>160</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly/【2025年8月】月次数値.xlsx
+++ b/data/monthly/【2025年8月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="68">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -135,31 +134,113 @@
   </si>
   <si>
     <t>竹内歯科クリニック（審美ジルコニア）</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>actions:link_click</t>
+  </si>
+  <si>
+    <t>recently_completed</t>
+  </si>
+  <si>
+    <t>美酒食彩GANAR</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -167,36 +248,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,14 +566,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y21"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,7 +647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -619,7 +697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -669,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -719,7 +797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -769,18 +847,1140 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6">
+        <v>2033</v>
+      </c>
+      <c r="I6">
+        <v>3.4363009999999998</v>
+      </c>
+      <c r="J6">
+        <v>87.269841270000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>5498</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6">
+        <v>6986</v>
+      </c>
+      <c r="P6">
+        <v>787.00257699999997</v>
+      </c>
+      <c r="Q6">
+        <v>63</v>
+      </c>
+      <c r="S6">
+        <v>87.269841</v>
+      </c>
+      <c r="T6">
+        <v>0.90180400000000005</v>
+      </c>
+      <c r="U6">
+        <v>66</v>
+      </c>
+      <c r="V6">
+        <v>0.944747</v>
+      </c>
+      <c r="W6">
+        <v>83.303030000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>99</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7">
+        <v>5302</v>
+      </c>
+      <c r="I7">
+        <v>1.4458690000000001</v>
+      </c>
+      <c r="J7">
+        <v>59.2020202</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>5861</v>
+      </c>
+      <c r="N7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7">
+        <v>7666</v>
+      </c>
+      <c r="P7">
+        <v>764.54474300000004</v>
+      </c>
+      <c r="Q7">
+        <v>99</v>
+      </c>
+      <c r="S7">
+        <v>59.202019999999997</v>
+      </c>
+      <c r="T7">
+        <v>1.291417</v>
+      </c>
+      <c r="U7">
+        <v>106</v>
+      </c>
+      <c r="V7">
+        <v>1.3827290000000001</v>
+      </c>
+      <c r="W7">
+        <v>55.292453000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>111</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8">
+        <v>4778</v>
+      </c>
+      <c r="I8">
+        <v>1.360193</v>
+      </c>
+      <c r="J8">
+        <v>53.1981982</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>5905</v>
+      </c>
+      <c r="N8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8">
+        <v>6499</v>
+      </c>
+      <c r="P8">
+        <v>908.60132299999998</v>
+      </c>
+      <c r="Q8">
+        <v>111</v>
+      </c>
+      <c r="S8">
+        <v>53.198197999999998</v>
+      </c>
+      <c r="T8">
+        <v>1.7079549999999999</v>
+      </c>
+      <c r="U8">
+        <v>127</v>
+      </c>
+      <c r="V8">
+        <v>1.9541470000000001</v>
+      </c>
+      <c r="W8">
+        <v>46.496062999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>342</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9">
+        <v>4178</v>
+      </c>
+      <c r="I9">
+        <v>1.398755</v>
+      </c>
+      <c r="J9">
+        <v>16.58187135</v>
+      </c>
+      <c r="K9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>5671</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9">
+        <v>5844</v>
+      </c>
+      <c r="P9">
+        <v>970.39698799999996</v>
+      </c>
+      <c r="Q9">
+        <v>342</v>
+      </c>
+      <c r="S9">
+        <v>16.581871</v>
+      </c>
+      <c r="T9">
+        <v>5.8521559999999999</v>
+      </c>
+      <c r="U9">
+        <v>379</v>
+      </c>
+      <c r="V9">
+        <v>6.485284</v>
+      </c>
+      <c r="W9">
+        <v>14.963061</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>160</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10">
+        <v>4003</v>
+      </c>
+      <c r="I10">
+        <v>1.571072</v>
+      </c>
+      <c r="J10">
+        <v>38.15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>6104</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10">
+        <v>6289</v>
+      </c>
+      <c r="P10">
+        <v>970.58355900000004</v>
+      </c>
+      <c r="Q10">
+        <v>160</v>
+      </c>
+      <c r="S10">
+        <v>38.15</v>
+      </c>
+      <c r="T10">
+        <v>2.5441250000000002</v>
+      </c>
+      <c r="U10">
+        <v>174</v>
+      </c>
+      <c r="V10">
+        <v>2.7667359999999999</v>
+      </c>
+      <c r="W10">
+        <v>35.080460000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11">
+        <v>152</v>
+      </c>
+      <c r="G11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11">
+        <v>4291</v>
+      </c>
+      <c r="I11">
+        <v>1.7119549999999999</v>
+      </c>
+      <c r="J11">
+        <v>36.657894740000003</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>5572</v>
+      </c>
+      <c r="N11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11">
+        <v>7346</v>
+      </c>
+      <c r="P11">
+        <v>758.50803199999996</v>
+      </c>
+      <c r="Q11">
+        <v>152</v>
+      </c>
+      <c r="S11">
+        <v>36.657895000000003</v>
+      </c>
+      <c r="T11">
+        <v>2.069153</v>
+      </c>
+      <c r="U11">
+        <v>188</v>
+      </c>
+      <c r="V11">
+        <v>2.5592160000000002</v>
+      </c>
+      <c r="W11">
+        <v>29.638297999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12">
+        <v>219</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12">
+        <v>3802</v>
+      </c>
+      <c r="I12">
+        <v>1.9560759999999999</v>
+      </c>
+      <c r="J12">
+        <v>25.319634700000002</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>5545</v>
+      </c>
+      <c r="N12" t="s">
+        <v>57</v>
+      </c>
+      <c r="O12">
+        <v>7437</v>
+      </c>
+      <c r="P12">
+        <v>745.59634300000005</v>
+      </c>
+      <c r="Q12">
+        <v>219</v>
+      </c>
+      <c r="S12">
+        <v>25.319635000000002</v>
+      </c>
+      <c r="T12">
+        <v>2.9447359999999998</v>
+      </c>
+      <c r="U12">
+        <v>267</v>
+      </c>
+      <c r="V12">
+        <v>3.590157</v>
+      </c>
+      <c r="W12">
+        <v>20.767790000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>245</v>
+      </c>
+      <c r="G13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13">
+        <v>4039</v>
+      </c>
+      <c r="I13">
+        <v>1.449864</v>
+      </c>
+      <c r="J13">
+        <v>23.636734690000001</v>
+      </c>
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>5791</v>
+      </c>
+      <c r="N13" t="s">
+        <v>57</v>
+      </c>
+      <c r="O13">
+        <v>5856</v>
+      </c>
+      <c r="P13">
+        <v>988.90027299999997</v>
+      </c>
+      <c r="Q13">
+        <v>245</v>
+      </c>
+      <c r="S13">
+        <v>23.636735000000002</v>
+      </c>
+      <c r="T13">
+        <v>4.1837429999999998</v>
+      </c>
+      <c r="U13">
+        <v>263</v>
+      </c>
+      <c r="V13">
+        <v>4.4911199999999996</v>
+      </c>
+      <c r="W13">
+        <v>22.019010999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14">
+        <v>203</v>
+      </c>
+      <c r="G14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14">
+        <v>3014</v>
+      </c>
+      <c r="I14">
+        <v>1.606503</v>
+      </c>
+      <c r="J14">
+        <v>29.669950740000001</v>
+      </c>
+      <c r="K14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>6023</v>
+      </c>
+      <c r="N14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14">
+        <v>4842</v>
+      </c>
+      <c r="P14">
+        <v>1243.9074760000001</v>
+      </c>
+      <c r="Q14">
+        <v>203</v>
+      </c>
+      <c r="S14">
+        <v>29.669951000000001</v>
+      </c>
+      <c r="T14">
+        <v>4.192482</v>
+      </c>
+      <c r="U14">
+        <v>227</v>
+      </c>
+      <c r="V14">
+        <v>4.6881449999999996</v>
+      </c>
+      <c r="W14">
+        <v>26.53304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <v>125</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15">
+        <v>4902</v>
+      </c>
+      <c r="I15">
+        <v>1.297226</v>
+      </c>
+      <c r="J15">
+        <v>51.152000000000001</v>
+      </c>
+      <c r="K15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>6394</v>
+      </c>
+      <c r="N15" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15">
+        <v>6359</v>
+      </c>
+      <c r="P15">
+        <v>1005.50401</v>
+      </c>
+      <c r="Q15">
+        <v>125</v>
+      </c>
+      <c r="S15">
+        <v>51.152000000000001</v>
+      </c>
+      <c r="T15">
+        <v>1.9657180000000001</v>
+      </c>
+      <c r="U15">
+        <v>130</v>
+      </c>
+      <c r="V15">
+        <v>2.0443470000000001</v>
+      </c>
+      <c r="W15">
+        <v>49.184615000000001</v>
+      </c>
+      <c r="X15">
+        <v>63</v>
+      </c>
+      <c r="Y15">
+        <v>101.492063</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16">
+        <v>128</v>
+      </c>
+      <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16">
+        <v>3560</v>
+      </c>
+      <c r="I16">
+        <v>1.7011240000000001</v>
+      </c>
+      <c r="J16">
+        <v>44.1484375</v>
+      </c>
+      <c r="K16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>5651</v>
+      </c>
+      <c r="N16" t="s">
+        <v>52</v>
+      </c>
+      <c r="O16">
+        <v>6056</v>
+      </c>
+      <c r="P16">
+        <v>933.12417400000004</v>
+      </c>
+      <c r="Q16">
+        <v>128</v>
+      </c>
+      <c r="S16">
+        <v>44.148437999999999</v>
+      </c>
+      <c r="T16">
+        <v>2.1136059999999999</v>
+      </c>
+      <c r="U16">
+        <v>152</v>
+      </c>
+      <c r="V16">
+        <v>2.5099079999999998</v>
+      </c>
+      <c r="W16">
+        <v>37.177632000000003</v>
+      </c>
+      <c r="X16">
+        <v>107</v>
+      </c>
+      <c r="Y16">
+        <v>52.813084000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17">
+        <v>156</v>
+      </c>
+      <c r="G17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17">
+        <v>3678</v>
+      </c>
+      <c r="I17">
+        <v>1.47689</v>
+      </c>
+      <c r="J17">
+        <v>33.11538462</v>
+      </c>
+      <c r="K17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>5166</v>
+      </c>
+      <c r="N17" t="s">
+        <v>47</v>
+      </c>
+      <c r="O17">
+        <v>5432</v>
+      </c>
+      <c r="P17">
+        <v>951.03092800000002</v>
+      </c>
+      <c r="Q17">
+        <v>156</v>
+      </c>
+      <c r="S17">
+        <v>33.115385000000003</v>
+      </c>
+      <c r="T17">
+        <v>2.8718699999999999</v>
+      </c>
+      <c r="U17">
+        <v>194</v>
+      </c>
+      <c r="V17">
+        <v>3.5714290000000002</v>
+      </c>
+      <c r="W17">
+        <v>26.628865999999999</v>
+      </c>
+      <c r="X17">
+        <v>122</v>
+      </c>
+      <c r="Y17">
+        <v>42.344262000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18">
+        <v>207</v>
+      </c>
+      <c r="G18" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18">
+        <v>4560</v>
+      </c>
+      <c r="I18">
+        <v>1.6122810000000001</v>
+      </c>
+      <c r="J18">
+        <v>25.140096620000001</v>
+      </c>
+      <c r="K18" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>5204</v>
+      </c>
+      <c r="N18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O18">
+        <v>7352</v>
+      </c>
+      <c r="P18">
+        <v>707.83460300000002</v>
+      </c>
+      <c r="Q18">
+        <v>207</v>
+      </c>
+      <c r="S18">
+        <v>25.140097000000001</v>
+      </c>
+      <c r="T18">
+        <v>2.8155600000000001</v>
+      </c>
+      <c r="U18">
+        <v>260</v>
+      </c>
+      <c r="V18">
+        <v>3.5364529999999998</v>
+      </c>
+      <c r="W18">
+        <v>20.015384999999998</v>
+      </c>
+      <c r="X18">
+        <v>176</v>
+      </c>
+      <c r="Y18">
+        <v>29.568182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19">
+        <v>5760</v>
+      </c>
+      <c r="I19">
+        <v>1.4737849999999999</v>
+      </c>
+      <c r="J19">
+        <v>59.833333330000002</v>
+      </c>
+      <c r="K19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>5385</v>
+      </c>
+      <c r="N19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O19">
+        <v>8489</v>
+      </c>
+      <c r="P19">
+        <v>634.35033599999997</v>
+      </c>
+      <c r="Q19">
+        <v>90</v>
+      </c>
+      <c r="S19">
+        <v>59.833333000000003</v>
+      </c>
+      <c r="T19">
+        <v>1.0601959999999999</v>
+      </c>
+      <c r="U19">
+        <v>107</v>
+      </c>
+      <c r="V19">
+        <v>1.2604550000000001</v>
+      </c>
+      <c r="W19">
+        <v>50.327103000000001</v>
+      </c>
+      <c r="X19">
+        <v>63</v>
+      </c>
+      <c r="Y19">
+        <v>85.476190000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20">
+        <v>98</v>
+      </c>
+      <c r="G20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20">
+        <v>4689</v>
+      </c>
+      <c r="I20">
+        <v>1.460866</v>
+      </c>
+      <c r="J20">
+        <v>48.673469390000001</v>
+      </c>
+      <c r="K20" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>4770</v>
+      </c>
+      <c r="N20" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20">
+        <v>6850</v>
+      </c>
+      <c r="P20">
+        <v>696.35036500000001</v>
+      </c>
+      <c r="Q20">
+        <v>98</v>
+      </c>
+      <c r="S20">
+        <v>48.673468999999997</v>
+      </c>
+      <c r="T20">
+        <v>1.4306570000000001</v>
+      </c>
+      <c r="U20">
+        <v>102</v>
+      </c>
+      <c r="V20">
+        <v>1.4890509999999999</v>
+      </c>
+      <c r="W20">
+        <v>46.764705999999997</v>
+      </c>
+      <c r="X20">
+        <v>73</v>
+      </c>
+      <c r="Y20">
+        <v>65.342466000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21">
+        <v>57</v>
+      </c>
+      <c r="G21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21">
+        <v>1358</v>
+      </c>
+      <c r="I21">
+        <v>1.349043</v>
+      </c>
+      <c r="J21">
+        <v>21.543859650000002</v>
+      </c>
+      <c r="K21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1228</v>
+      </c>
+      <c r="N21" t="s">
+        <v>40</v>
+      </c>
+      <c r="O21">
+        <v>1832</v>
+      </c>
+      <c r="P21">
+        <v>670.30567699999995</v>
+      </c>
+      <c r="Q21">
+        <v>57</v>
+      </c>
+      <c r="S21">
+        <v>21.543859999999999</v>
+      </c>
+      <c r="T21">
+        <v>3.111354</v>
+      </c>
+      <c r="U21">
+        <v>60</v>
+      </c>
+      <c r="V21">
+        <v>3.275109</v>
+      </c>
+      <c r="W21">
+        <v>20.466667000000001</v>
+      </c>
+      <c r="X21">
+        <v>9</v>
+      </c>
+      <c r="Y21">
+        <v>136.444444</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>